--- a/AHP_Weights_and_ConsistencyCheck.xlsx
+++ b/AHP_Weights_and_ConsistencyCheck.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\petke\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lia\Nextcloud\Data Analytics für Circular Digital Health\WI2026\Quotient\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F81CB230-AF26-4E04-A386-398577F3DF41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16A0D15C-1B53-41F1-92D9-854DECC79E8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-60" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-6900" windowWidth="16440" windowHeight="28320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AHP" sheetId="1" r:id="rId1"/>
@@ -35,15 +35,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="19">
   <si>
-    <t>AHP-Gewichtungsrechner (Paarvergleichsmatrix → Gewichte + Konsistenzcheck)</t>
-  </si>
-  <si>
-    <t>Eingabe: Trage nur die Werte OBERHALB der Diagonale ein (gelb). Unterhalb wird automatisch als Kehrwert berechnet.</t>
-  </si>
-  <si>
-    <t>1) Paarvergleichsmatrix A (Saaty-AHP)</t>
-  </si>
-  <si>
     <t>C1</t>
   </si>
   <si>
@@ -68,15 +59,6 @@
     <t>λ_i</t>
   </si>
   <si>
-    <t>Spaltensumme</t>
-  </si>
-  <si>
-    <t>2) Normierte Matrix N (jede Spalte durch Spaltensumme teilen)</t>
-  </si>
-  <si>
-    <t>3) Konsistenzcheck (AHP)</t>
-  </si>
-  <si>
     <t>λ_max</t>
   </si>
   <si>
@@ -89,7 +71,25 @@
     <t>CR</t>
   </si>
   <si>
-    <t>Interpretation: CR &lt; 0,10 = akzeptabel; CR ≥ 0,10 = Paarvergleiche prüfen.</t>
+    <t>1) Pair Comparison Matrix A (Saaty-AHP)</t>
+  </si>
+  <si>
+    <t>3) Consistency check (AHP)</t>
+  </si>
+  <si>
+    <t>Interpretation: CR &lt; 0,10 = acceptable; CR ≥ 0,10 = check pair comparison.</t>
+  </si>
+  <si>
+    <t>2) Normed Matrix N (divide each column by sum of coulm)</t>
+  </si>
+  <si>
+    <t>Input: Enter only the values ABOVE the diagonal (yellow). Below is automatically calculated as a reciprocal.</t>
+  </si>
+  <si>
+    <t>SUM</t>
+  </si>
+  <si>
+    <t>AHP-Weight calculator (Pair Comparison Matrix → Weights + Consistency check) by Florian Petke 2026</t>
   </si>
 </sst>
 </file>
@@ -99,7 +99,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -139,13 +139,6 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="9">
@@ -215,47 +208,45 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="8" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -447,7 +438,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J29"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="6" width="11" customWidth="1"/>
@@ -456,8 +447,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="10" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -471,7 +462,7 @@
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B2" s="11"/>
       <c r="C2" s="11"/>
@@ -485,7 +476,7 @@
     </row>
     <row r="4" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="B4" s="11"/>
       <c r="C4" s="11"/>
@@ -498,229 +489,229 @@
       <c r="J4" s="11"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="F5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="H5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="I5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="J5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>10</v>
-      </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="3">
+        <v>1</v>
+      </c>
+      <c r="C6" s="4">
         <v>3</v>
       </c>
-      <c r="B6" s="2">
-        <v>1</v>
-      </c>
-      <c r="C6" s="3">
+      <c r="D6" s="4">
+        <v>4</v>
+      </c>
+      <c r="E6" s="4">
         <v>3</v>
       </c>
-      <c r="D6" s="3">
-        <v>4</v>
-      </c>
-      <c r="E6" s="3">
-        <v>3</v>
-      </c>
-      <c r="F6" s="3">
-        <v>1</v>
-      </c>
-      <c r="H6" s="4">
+      <c r="F6" s="4">
+        <v>1</v>
+      </c>
+      <c r="H6" s="5">
         <f>AVERAGE(B15:F15)</f>
         <v>0.33985437363092597</v>
       </c>
-      <c r="I6" s="4">
+      <c r="I6" s="5">
         <f>B6*$H$6+C6*$H$7+D6*$H$8+E6*$H$9+F6*$H$10</f>
         <v>1.7137535711322323</v>
       </c>
-      <c r="J6" s="4">
+      <c r="J6" s="5">
         <f>IF($H6=0,"",I6/$H6)</f>
         <v>5.0426114951026912</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="5">
+      <c r="A7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="6">
         <f>IF(C6="","",1/C6)</f>
         <v>0.33333333333333331</v>
       </c>
-      <c r="C7" s="2">
-        <v>1</v>
-      </c>
-      <c r="D7" s="3">
+      <c r="C7" s="3">
+        <v>1</v>
+      </c>
+      <c r="D7" s="4">
         <v>2</v>
       </c>
-      <c r="E7" s="3">
-        <v>1</v>
-      </c>
-      <c r="F7" s="3">
+      <c r="E7" s="4">
+        <v>1</v>
+      </c>
+      <c r="F7" s="4">
         <v>0.33329999999999999</v>
       </c>
-      <c r="H7" s="4">
+      <c r="H7" s="5">
         <f>AVERAGE(B16:F16)</f>
         <v>0.12353891570018709</v>
       </c>
-      <c r="I7" s="4">
+      <c r="I7" s="5">
         <f>B7*$H$6+C7*$H$7+D7*$H$8+E7*$H$9+F7*$H$10</f>
         <v>0.62003939661244512</v>
       </c>
-      <c r="J7" s="4">
+      <c r="J7" s="5">
         <f>IF($H7=0,"",I7/$H7)</f>
         <v>5.0189804006148169</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8" s="5">
+      <c r="A8" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8" s="6">
         <f>IF(D6="","",1/D6)</f>
         <v>0.25</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8" s="6">
         <f>IF(D7="","",1/D7)</f>
         <v>0.5</v>
       </c>
-      <c r="D8" s="2">
-        <v>1</v>
-      </c>
-      <c r="E8" s="3">
+      <c r="D8" s="3">
+        <v>1</v>
+      </c>
+      <c r="E8" s="4">
         <v>0.5</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="4">
         <v>0.25</v>
       </c>
-      <c r="H8" s="4">
+      <c r="H8" s="5">
         <f>AVERAGE(B17:F17)</f>
         <v>7.3199302777161274E-2</v>
       </c>
-      <c r="I8" s="4">
+      <c r="I8" s="5">
         <f>B8*$H$6+C8*$H$7+D8*$H$8+E8*$H$9+F8*$H$10</f>
         <v>0.36666893493296454</v>
       </c>
-      <c r="J8" s="4">
+      <c r="J8" s="5">
         <f>IF($H8=0,"",I8/$H8)</f>
         <v>5.0091861673765559</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" s="5">
+      <c r="A9" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="6">
         <f>IF(E6="","",1/E6)</f>
         <v>0.33333333333333331</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C9" s="6">
         <f>IF(E7="","",1/E7)</f>
         <v>1</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D9" s="6">
         <f>IF(E8="","",1/E8)</f>
         <v>2</v>
       </c>
-      <c r="E9" s="2">
-        <v>1</v>
-      </c>
-      <c r="F9" s="3">
+      <c r="E9" s="3">
+        <v>1</v>
+      </c>
+      <c r="F9" s="4">
         <v>0.33329999999999999</v>
       </c>
-      <c r="H9" s="4">
+      <c r="H9" s="5">
         <f>AVERAGE(B18:F18)</f>
         <v>0.12353891570018709</v>
       </c>
-      <c r="I9" s="4">
+      <c r="I9" s="5">
         <f>B9*$H$6+C9*$H$7+D9*$H$8+E9*$H$9+F9*$H$10</f>
         <v>0.62003939661244512</v>
       </c>
-      <c r="J9" s="4">
+      <c r="J9" s="5">
         <f>IF($H9=0,"",I9/$H9)</f>
         <v>5.0189804006148169</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" s="5">
+      <c r="A10" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" s="6">
         <f>IF(F6="","",1/F6)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="5">
+      <c r="C10" s="6">
         <f>IF(F7="","",1/F7)</f>
         <v>3.0003000300030003</v>
       </c>
-      <c r="D10" s="5">
+      <c r="D10" s="6">
         <f>IF(F8="","",1/F8)</f>
         <v>4</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E10" s="6">
         <f>IF(F9="","",1/F9)</f>
         <v>3.0003000300030003</v>
       </c>
-      <c r="F10" s="2">
-        <v>1</v>
-      </c>
-      <c r="H10" s="4">
+      <c r="F10" s="3">
+        <v>1</v>
+      </c>
+      <c r="H10" s="5">
         <f>AVERAGE(B19:F19)</f>
         <v>0.33986849219153864</v>
       </c>
-      <c r="I10" s="4">
+      <c r="I10" s="5">
         <f>B10*$H$6+C10*$H$7+D10*$H$8+E10*$H$9+F10*$H$10</f>
         <v>1.7138277018947286</v>
       </c>
-      <c r="J10" s="4">
+      <c r="J10" s="5">
         <f>IF($H10=0,"",I10/$H10)</f>
         <v>5.0426201347575104</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" s="4">
+      <c r="A11" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="5">
         <f>SUM(B6:B10)</f>
         <v>2.9166666666666665</v>
       </c>
-      <c r="C11" s="4">
+      <c r="C11" s="5">
         <f>SUM(C6:C10)</f>
         <v>8.5003000300030003</v>
       </c>
-      <c r="D11" s="4">
+      <c r="D11" s="5">
         <f>SUM(D6:D10)</f>
         <v>13</v>
       </c>
-      <c r="E11" s="4">
+      <c r="E11" s="5">
         <f>SUM(E6:E10)</f>
         <v>8.5003000300030003</v>
       </c>
-      <c r="F11" s="4">
+      <c r="F11" s="5">
         <f>SUM(F6:F10)</f>
         <v>2.9165999999999999</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -733,143 +724,143 @@
       <c r="J13" s="11"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="F14" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D14" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B15" s="5">
+      <c r="A15" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B15" s="6">
         <f>IF(B11=0,"",B6/B11)</f>
         <v>0.34285714285714286</v>
       </c>
-      <c r="C15" s="5">
+      <c r="C15" s="6">
         <f>IF(C11=0,"",C6/C11)</f>
         <v>0.35292871891710642</v>
       </c>
-      <c r="D15" s="5">
+      <c r="D15" s="6">
         <f>IF(D11=0,"",D6/D11)</f>
         <v>0.30769230769230771</v>
       </c>
-      <c r="E15" s="5">
+      <c r="E15" s="6">
         <f>IF(E11=0,"",E6/E11)</f>
         <v>0.35292871891710642</v>
       </c>
-      <c r="F15" s="5">
+      <c r="F15" s="6">
         <f>IF(F11=0,"",F6/F11)</f>
         <v>0.34286497977096619</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B16" s="5">
+      <c r="A16" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B16" s="6">
         <f>IF(B11=0,"",B7/B11)</f>
         <v>0.11428571428571428</v>
       </c>
-      <c r="C16" s="5">
+      <c r="C16" s="6">
         <f>IF(C11=0,"",C7/C11)</f>
         <v>0.11764290630570214</v>
       </c>
-      <c r="D16" s="5">
+      <c r="D16" s="6">
         <f>IF(D11=0,"",D7/D11)</f>
         <v>0.15384615384615385</v>
       </c>
-      <c r="E16" s="5">
+      <c r="E16" s="6">
         <f>IF(E11=0,"",E7/E11)</f>
         <v>0.11764290630570214</v>
       </c>
-      <c r="F16" s="5">
+      <c r="F16" s="6">
         <f>IF(F11=0,"",F7/F11)</f>
         <v>0.11427689775766303</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B17" s="5">
+      <c r="A17" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B17" s="6">
         <f>IF(B11=0,"",B8/B11)</f>
         <v>8.5714285714285715E-2</v>
       </c>
-      <c r="C17" s="5">
+      <c r="C17" s="6">
         <f>IF(C11=0,"",C8/C11)</f>
         <v>5.8821453152851068E-2</v>
       </c>
-      <c r="D17" s="5">
+      <c r="D17" s="6">
         <f>IF(D11=0,"",D8/D11)</f>
         <v>7.6923076923076927E-2</v>
       </c>
-      <c r="E17" s="5">
+      <c r="E17" s="6">
         <f>IF(E11=0,"",E8/E11)</f>
         <v>5.8821453152851068E-2</v>
       </c>
-      <c r="F17" s="5">
+      <c r="F17" s="6">
         <f>IF(F11=0,"",F8/F11)</f>
         <v>8.5716244942741548E-2</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B18" s="5">
+      <c r="A18" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B18" s="6">
         <f>IF(B11=0,"",B9/B11)</f>
         <v>0.11428571428571428</v>
       </c>
-      <c r="C18" s="5">
+      <c r="C18" s="6">
         <f>IF(C11=0,"",C9/C11)</f>
         <v>0.11764290630570214</v>
       </c>
-      <c r="D18" s="5">
+      <c r="D18" s="6">
         <f>IF(D11=0,"",D9/D11)</f>
         <v>0.15384615384615385</v>
       </c>
-      <c r="E18" s="5">
+      <c r="E18" s="6">
         <f>IF(E11=0,"",E9/E11)</f>
         <v>0.11764290630570214</v>
       </c>
-      <c r="F18" s="5">
+      <c r="F18" s="6">
         <f>IF(F11=0,"",F9/F11)</f>
         <v>0.11427689775766303</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B19" s="5">
+      <c r="A19" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" s="6">
         <f>IF(B11=0,"",B10/B11)</f>
         <v>0.34285714285714286</v>
       </c>
-      <c r="C19" s="5">
+      <c r="C19" s="6">
         <f>IF(C11=0,"",C10/C11)</f>
         <v>0.35296401531863825</v>
       </c>
-      <c r="D19" s="5">
+      <c r="D19" s="6">
         <f>IF(D11=0,"",D10/D11)</f>
         <v>0.30769230769230771</v>
       </c>
-      <c r="E19" s="5">
+      <c r="E19" s="6">
         <f>IF(E11=0,"",E10/E11)</f>
         <v>0.35296401531863825</v>
       </c>
-      <c r="F19" s="5">
+      <c r="F19" s="6">
         <f>IF(F11=0,"",F10/F11)</f>
         <v>0.34286497977096619</v>
       </c>
@@ -889,43 +880,43 @@
       <c r="J21" s="11"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B22" s="8">
+      <c r="A22" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B22" s="9">
         <f>AVERAGE(J6:J10)</f>
         <v>5.0264757196932788</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B23" s="8">
+      <c r="A23" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="9">
         <f>(B22-5)/4</f>
         <v>6.6189299233196941E-3</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B24" s="9">
+      <c r="A24" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B24" s="10">
         <v>1.1200000000000001</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B25" s="8">
+      <c r="A25" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B25" s="9">
         <f>IF(B24=0,"",B23/B24)</f>
         <v>5.9097588601068687E-3</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="12" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
